--- a/C_mass_sop_factory/data/output/Bulk_Create_FATHERDAY_DADJOKEJAR.xlsx
+++ b/C_mass_sop_factory/data/output/Bulk_Create_FATHERDAY_DADJOKEJAR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2378" uniqueCount="139">
   <si>
     <t>Product</t>
   </si>
@@ -121,124 +121,316 @@
     <t>Create</t>
   </si>
   <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_dad joke jar gift for dad_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_funny dad joke jar_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_dad joke cards in a jar_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_dad joke gift from daughter_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_dad joke gift from kids_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_dad joke kit gift set_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_funny jar gift for dad_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_gag gift dad joke jar_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_dad humor gift jar_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_joke jar for dad_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_fathers day gift funny_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_fathers day gag gift_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_funny fathers day gifts_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad jokes_30TRP</t>
-  </si>
-  <si>
-    <t>FATHERDAY_DADJOKEJAR_KT_phrase_dad jokes_30TRP</t>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_fathers_day_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_birthday_gift_for_dad_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_jokes_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_gift_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_thoughtful_gifts_for_men_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_funny_dad_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_gifts_for_dad_birthday_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_joke_button_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_birthday_gifts_from_daughter_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_gifts_for_dad_from_daughter_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_birthday_card_for_dad_from_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_girl_dad_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_gifts_for_dads_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_birthday_for_dad_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_birthday_gift_for_dad_from_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_funny_gift_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_boy_dad_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_gifts_for_birthday_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_gifts_from_daughter_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_birthday_card_from_daughter_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_gifts_for_dads_birthday_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_funny_birthday_card_for_dad_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_presents_for_dad_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dads_birthday_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_birthday_dad_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_office_gifts_for_men_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_stuff_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_birthday_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_father_day_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_best_dad_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_birthday_gifts_for_dad_from_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_football_stuffed_animal_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_fathers_birthday_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_father_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_birthday_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_father_daughter_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_dad_birthday_gift_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_cool_gadgets_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_fathers_day_gifts_for_dad_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_gag_gifts_for_men_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_birthday_gifts_for_dad_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_birthday_gift_for_men_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_gift_for_dad_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_funny_gifts_for_men_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_new_dad_gifts_50T</t>
+  </si>
+  <si>
+    <t>FATHERDAY_DADJOKEJAR_KT_exact_birthday_card_for_dad_50T</t>
   </si>
   <si>
     <t>253189447671739</t>
   </si>
   <si>
-    <t>dad joke jar gift for dad</t>
-  </si>
-  <si>
-    <t>funny dad joke jar</t>
-  </si>
-  <si>
-    <t>dad joke cards in a jar</t>
-  </si>
-  <si>
-    <t>dad joke gift from daughter</t>
-  </si>
-  <si>
-    <t>dad joke gift from kids</t>
-  </si>
-  <si>
-    <t>dad joke kit gift set</t>
-  </si>
-  <si>
-    <t>funny jar gift for dad</t>
-  </si>
-  <si>
-    <t>gag gift dad joke jar</t>
-  </si>
-  <si>
-    <t>dad humor gift jar</t>
-  </si>
-  <si>
-    <t>joke jar for dad</t>
-  </si>
-  <si>
-    <t>fathers day gift funny</t>
-  </si>
-  <si>
-    <t>fathers day gag gift</t>
-  </si>
-  <si>
-    <t>funny fathers day gifts</t>
+    <t>fathers day gifts</t>
+  </si>
+  <si>
+    <t>birthday gift for dad</t>
   </si>
   <si>
     <t>dad jokes</t>
   </si>
   <si>
-    <t>20260418</t>
-  </si>
-  <si>
-    <t>MANUAL</t>
-  </si>
-  <si>
-    <t>enabled</t>
+    <t>dad gifts</t>
+  </si>
+  <si>
+    <t>dad gift</t>
+  </si>
+  <si>
+    <t>thoughtful gifts for men</t>
+  </si>
+  <si>
+    <t>funny dad gifts</t>
+  </si>
+  <si>
+    <t>gifts for dad birthday</t>
+  </si>
+  <si>
+    <t>dad joke button</t>
+  </si>
+  <si>
+    <t>dad birthday gifts from daughter</t>
+  </si>
+  <si>
+    <t>gifts for dad from daughter</t>
+  </si>
+  <si>
+    <t>birthday card for dad from daughter</t>
+  </si>
+  <si>
+    <t>girl dad gifts</t>
+  </si>
+  <si>
+    <t>gifts for dads</t>
+  </si>
+  <si>
+    <t>birthday for dad</t>
+  </si>
+  <si>
+    <t>birthday gift for dad from daughter</t>
+  </si>
+  <si>
+    <t>funny gift</t>
+  </si>
+  <si>
+    <t>boy dad gifts</t>
+  </si>
+  <si>
+    <t>dad gifts for birthday</t>
+  </si>
+  <si>
+    <t>dad gifts from daughter</t>
+  </si>
+  <si>
+    <t>dad birthday card from daughter</t>
+  </si>
+  <si>
+    <t>gifts for dads birthday</t>
+  </si>
+  <si>
+    <t>funny birthday card for dad</t>
+  </si>
+  <si>
+    <t>presents for dad</t>
+  </si>
+  <si>
+    <t>dads birthday</t>
+  </si>
+  <si>
+    <t>birthday dad</t>
+  </si>
+  <si>
+    <t>office gifts for men</t>
+  </si>
+  <si>
+    <t>dad stuff</t>
+  </si>
+  <si>
+    <t>dad birthday</t>
+  </si>
+  <si>
+    <t>father day gifts</t>
+  </si>
+  <si>
+    <t>best dad gifts</t>
+  </si>
+  <si>
+    <t>birthday gifts for dad from daughter</t>
+  </si>
+  <si>
+    <t>football stuffed animal</t>
+  </si>
+  <si>
+    <t>fathers birthday gifts</t>
+  </si>
+  <si>
+    <t>father gifts</t>
+  </si>
+  <si>
+    <t>dad birthday gifts</t>
+  </si>
+  <si>
+    <t>father daughter gifts</t>
+  </si>
+  <si>
+    <t>dad birthday gift</t>
+  </si>
+  <si>
+    <t>cool gadgets</t>
+  </si>
+  <si>
+    <t>fathers day gifts for dad</t>
+  </si>
+  <si>
+    <t>gag gifts for men</t>
+  </si>
+  <si>
+    <t>birthday gifts for dad</t>
+  </si>
+  <si>
+    <t>birthday gift for men</t>
+  </si>
+  <si>
+    <t>gift for dad</t>
+  </si>
+  <si>
+    <t>funny gifts for men</t>
+  </si>
+  <si>
+    <t>new dad gifts</t>
+  </si>
+  <si>
+    <t>birthday card for dad</t>
+  </si>
+  <si>
+    <t>20260423</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>Enabled</t>
   </si>
   <si>
     <t>FATHERDAY_DADJOKEJAR</t>
   </si>
   <si>
-    <t>phrase</t>
-  </si>
-  <si>
     <t>exact</t>
   </si>
   <si>
     <t>Dynamic bids - down only</t>
   </si>
   <si>
-    <t>placement top</t>
-  </si>
-  <si>
-    <t>placementProductPage</t>
-  </si>
-  <si>
-    <t>placementRestOfSearch</t>
+    <t>Placement Top</t>
+  </si>
+  <si>
+    <t>Placement Product Page</t>
+  </si>
+  <si>
+    <t>Placement Rest Of Search</t>
   </si>
 </sst>
 </file>
@@ -600,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB106"/>
+  <dimension ref="A1:AB330"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="28" width="20.7109375" style="1" customWidth="1"/>
@@ -706,25 +898,25 @@
         <v>35</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P2" s="1">
         <v>5</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:28">
@@ -741,13 +933,13 @@
         <v>35</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA3" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -764,13 +956,13 @@
         <v>35</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA4" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:28">
@@ -787,13 +979,13 @@
         <v>35</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA5" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -813,13 +1005,13 @@
         <v>35</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U6" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -839,10 +1031,10 @@
         <v>35</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -862,16 +1054,16 @@
         <v>35</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V8" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -888,25 +1080,25 @@
         <v>36</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P9" s="1">
         <v>5</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -923,13 +1115,13 @@
         <v>36</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA10" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -946,13 +1138,13 @@
         <v>36</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA11" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -969,13 +1161,13 @@
         <v>36</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA12" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -995,13 +1187,13 @@
         <v>36</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U13" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -1021,10 +1213,10 @@
         <v>36</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:28">
@@ -1044,16 +1236,16 @@
         <v>36</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V15" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -1070,25 +1262,25 @@
         <v>37</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>37</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P16" s="1">
         <v>5</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -1105,13 +1297,13 @@
         <v>37</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA17" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -1128,13 +1320,13 @@
         <v>37</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA18" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -1151,13 +1343,13 @@
         <v>37</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA19" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -1177,13 +1369,13 @@
         <v>37</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U20" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -1203,10 +1395,10 @@
         <v>37</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -1226,16 +1418,16 @@
         <v>37</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V22" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -1252,25 +1444,25 @@
         <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>38</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P23" s="1">
         <v>5</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -1287,13 +1479,13 @@
         <v>38</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA24" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -1310,13 +1502,13 @@
         <v>38</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA25" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -1333,13 +1525,13 @@
         <v>38</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA26" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -1359,13 +1551,13 @@
         <v>38</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U27" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -1385,10 +1577,10 @@
         <v>38</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -1408,16 +1600,16 @@
         <v>38</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V29" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -1434,25 +1626,25 @@
         <v>39</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>39</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P30" s="1">
         <v>5</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -1469,13 +1661,13 @@
         <v>39</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA31" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -1492,13 +1684,13 @@
         <v>39</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA32" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -1515,13 +1707,13 @@
         <v>39</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA33" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -1541,13 +1733,13 @@
         <v>39</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U34" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:27">
@@ -1567,10 +1759,10 @@
         <v>39</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -1590,16 +1782,16 @@
         <v>39</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V36" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -1616,25 +1808,25 @@
         <v>40</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>40</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P37" s="1">
         <v>5</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -1651,13 +1843,13 @@
         <v>40</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA38" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -1674,13 +1866,13 @@
         <v>40</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA39" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -1697,13 +1889,13 @@
         <v>40</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA40" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -1723,13 +1915,13 @@
         <v>40</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U41" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -1749,10 +1941,10 @@
         <v>40</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -1772,16 +1964,16 @@
         <v>40</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V43" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="X43" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -1798,25 +1990,25 @@
         <v>41</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>41</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P44" s="1">
         <v>5</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:27">
@@ -1833,13 +2025,13 @@
         <v>41</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z45" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA45" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -1856,13 +2048,13 @@
         <v>41</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA46" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -1879,13 +2071,13 @@
         <v>41</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z47" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA47" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -1905,13 +2097,13 @@
         <v>41</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U48" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -1931,10 +2123,10 @@
         <v>41</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -1954,16 +2146,16 @@
         <v>41</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V50" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -1980,25 +2172,25 @@
         <v>42</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>42</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P51" s="1">
         <v>5</v>
       </c>
       <c r="Y51" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -2015,13 +2207,13 @@
         <v>42</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z52" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA52" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -2038,13 +2230,13 @@
         <v>42</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z53" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA53" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -2061,13 +2253,13 @@
         <v>42</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z54" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA54" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -2087,13 +2279,13 @@
         <v>42</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U55" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -2113,10 +2305,10 @@
         <v>42</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:27">
@@ -2136,16 +2328,16 @@
         <v>42</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V57" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="X57" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -2162,25 +2354,25 @@
         <v>43</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>43</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P58" s="1">
         <v>5</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="59" spans="1:27">
@@ -2197,13 +2389,13 @@
         <v>43</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z59" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA59" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:27">
@@ -2220,13 +2412,13 @@
         <v>43</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z60" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA60" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:27">
@@ -2243,13 +2435,13 @@
         <v>43</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z61" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA61" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:27">
@@ -2269,13 +2461,13 @@
         <v>43</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U62" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -2295,10 +2487,10 @@
         <v>43</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:27">
@@ -2318,16 +2510,16 @@
         <v>43</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V64" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="X64" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:27">
@@ -2344,25 +2536,25 @@
         <v>44</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P65" s="1">
         <v>5</v>
       </c>
       <c r="Y65" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -2379,13 +2571,13 @@
         <v>44</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z66" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA66" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -2402,13 +2594,13 @@
         <v>44</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z67" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA67" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -2425,13 +2617,13 @@
         <v>44</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z68" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA68" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -2451,13 +2643,13 @@
         <v>44</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U69" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -2477,10 +2669,10 @@
         <v>44</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -2500,16 +2692,16 @@
         <v>44</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V71" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -2526,25 +2718,25 @@
         <v>45</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>45</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P72" s="1">
         <v>5</v>
       </c>
       <c r="Y72" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:27">
@@ -2561,13 +2753,13 @@
         <v>45</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z73" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA73" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -2584,13 +2776,13 @@
         <v>45</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z74" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA74" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -2607,13 +2799,13 @@
         <v>45</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z75" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA75" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -2633,13 +2825,13 @@
         <v>45</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U76" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -2659,10 +2851,10 @@
         <v>45</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -2682,16 +2874,16 @@
         <v>45</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V78" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W78" s="1" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="X78" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -2708,25 +2900,25 @@
         <v>46</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P79" s="1">
         <v>5</v>
       </c>
       <c r="Y79" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -2743,13 +2935,13 @@
         <v>46</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z80" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA80" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -2766,13 +2958,13 @@
         <v>46</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z81" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA81" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -2789,13 +2981,13 @@
         <v>46</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z82" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA82" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:27">
@@ -2815,13 +3007,13 @@
         <v>46</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U83" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:27">
@@ -2841,10 +3033,10 @@
         <v>46</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="85" spans="1:27">
@@ -2864,16 +3056,16 @@
         <v>46</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V85" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W85" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="X85" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86" spans="1:27">
@@ -2890,25 +3082,25 @@
         <v>47</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>47</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P86" s="1">
         <v>5</v>
       </c>
       <c r="Y86" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -2925,13 +3117,13 @@
         <v>47</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z87" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA87" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -2948,13 +3140,13 @@
         <v>47</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z88" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA88" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -2971,13 +3163,13 @@
         <v>47</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z89" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA89" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:27">
@@ -2997,13 +3189,13 @@
         <v>47</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U90" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="91" spans="1:27">
@@ -3023,10 +3215,10 @@
         <v>47</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q91" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="92" spans="1:27">
@@ -3046,16 +3238,16 @@
         <v>47</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V92" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W92" s="1" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="X92" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
     </row>
     <row r="93" spans="1:27">
@@ -3072,25 +3264,25 @@
         <v>48</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>48</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P93" s="1">
         <v>5</v>
       </c>
       <c r="Y93" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="94" spans="1:27">
@@ -3107,13 +3299,13 @@
         <v>48</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z94" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA94" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:27">
@@ -3130,13 +3322,13 @@
         <v>48</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z95" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA95" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:27">
@@ -3153,13 +3345,13 @@
         <v>48</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z96" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA96" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:27">
@@ -3179,13 +3371,13 @@
         <v>48</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U97" s="1">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:27">
@@ -3205,10 +3397,10 @@
         <v>48</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q98" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="99" spans="1:27">
@@ -3228,16 +3420,16 @@
         <v>48</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="V99" s="1">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W99" s="1" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
     </row>
     <row r="100" spans="1:27">
@@ -3254,25 +3446,25 @@
         <v>49</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>49</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="P100" s="1">
         <v>5</v>
       </c>
       <c r="Y100" s="1" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="101" spans="1:27">
@@ -3289,13 +3481,13 @@
         <v>49</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z101" s="1" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="AA101" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="102" spans="1:27">
@@ -3312,13 +3504,13 @@
         <v>49</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z102" s="1" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="AA102" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:27">
@@ -3335,13 +3527,13 @@
         <v>49</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Z103" s="1" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="AA103" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:27">
@@ -3361,13 +3553,13 @@
         <v>49</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="U104" s="1">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="105" spans="1:27">
@@ -3387,10 +3579,10 @@
         <v>49</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="Q105" s="1" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
     </row>
     <row r="106" spans="1:27">
@@ -3410,16 +3602,5840 @@
         <v>49</v>
       </c>
       <c r="O106" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V106" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W106" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="X106" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27">
+      <c r="A107" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P107" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y107" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27">
+      <c r="A108" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z108" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA108" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27">
+      <c r="A109" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z109" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA109" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27">
+      <c r="A110" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z110" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA110" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27">
+      <c r="A111" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U111" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27">
+      <c r="A112" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q112" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27">
+      <c r="A113" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V113" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W113" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="X113" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27">
+      <c r="A114" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P114" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y114" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27">
+      <c r="A115" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z115" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA115" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="116" spans="1:27">
+      <c r="A116" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z116" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:27">
+      <c r="A117" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z117" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:27">
+      <c r="A118" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U118" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="119" spans="1:27">
+      <c r="A119" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q119" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="120" spans="1:27">
+      <c r="A120" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V120" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W120" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="X120" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27">
+      <c r="A121" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P121" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y121" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="122" spans="1:27">
+      <c r="A122" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O122" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z122" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA122" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="123" spans="1:27">
+      <c r="A123" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z123" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:27">
+      <c r="A124" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O124" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z124" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:27">
+      <c r="A125" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O125" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U125" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:27">
+      <c r="A126" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O126" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q126" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="127" spans="1:27">
+      <c r="A127" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O127" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V127" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W127" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="X127" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="128" spans="1:27">
+      <c r="A128" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N128" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O128" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P128" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y128" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="129" spans="1:27">
+      <c r="A129" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O129" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z129" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA129" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="130" spans="1:27">
+      <c r="A130" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O130" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z130" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:27">
+      <c r="A131" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O131" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z131" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:27">
+      <c r="A132" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O132" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U132" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:27">
+      <c r="A133" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O133" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q133" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="1:27">
+      <c r="A134" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O134" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V134" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W134" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="X134" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:27">
+      <c r="A135" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N135" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O135" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P135" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y135" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:27">
+      <c r="A136" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z136" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA136" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="137" spans="1:27">
+      <c r="A137" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O137" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z137" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:27">
+      <c r="A138" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O138" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z138" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:27">
+      <c r="A139" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O139" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U139" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:27">
+      <c r="A140" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O140" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q140" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="141" spans="1:27">
+      <c r="A141" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V141" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W141" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="X141" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="142" spans="1:27">
+      <c r="A142" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O142" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P142" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y142" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="143" spans="1:27">
+      <c r="A143" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O143" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z143" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA143" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="144" spans="1:27">
+      <c r="A144" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O144" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z144" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:27">
+      <c r="A145" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O145" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z145" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:27">
+      <c r="A146" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O146" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U146" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:27">
+      <c r="A147" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O147" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q147" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="148" spans="1:27">
+      <c r="A148" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O148" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V148" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W148" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="X148" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="149" spans="1:27">
+      <c r="A149" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N149" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O149" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P149" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y149" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="150" spans="1:27">
+      <c r="A150" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O150" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z150" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA150" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="151" spans="1:27">
+      <c r="A151" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O151" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z151" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:27">
+      <c r="A152" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O152" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z152" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:27">
+      <c r="A153" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O153" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U153" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:27">
+      <c r="A154" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O154" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q154" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="155" spans="1:27">
+      <c r="A155" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O155" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V155" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W155" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="X155" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="156" spans="1:27">
+      <c r="A156" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L156" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N156" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O156" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P156" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y156" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="157" spans="1:27">
+      <c r="A157" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O157" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z157" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA157" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="158" spans="1:27">
+      <c r="A158" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O158" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z158" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:27">
+      <c r="A159" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O159" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z159" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:27">
+      <c r="A160" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O160" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U160" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:27">
+      <c r="A161" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O161" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q161" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="162" spans="1:27">
+      <c r="A162" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O162" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V162" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W162" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="X162" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="163" spans="1:27">
+      <c r="A163" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N163" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O163" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P163" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y163" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="164" spans="1:27">
+      <c r="A164" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O164" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z164" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA164" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="165" spans="1:27">
+      <c r="A165" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O165" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z165" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:27">
+      <c r="A166" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O166" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z166" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:27">
+      <c r="A167" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K167" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O167" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U167" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:27">
+      <c r="A168" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O168" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q168" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="169" spans="1:27">
+      <c r="A169" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O169" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V169" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W169" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="X169" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="170" spans="1:27">
+      <c r="A170" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L170" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N170" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O170" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P170" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y170" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="171" spans="1:27">
+      <c r="A171" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O171" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z171" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA171" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="172" spans="1:27">
+      <c r="A172" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O172" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z172" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:27">
+      <c r="A173" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O173" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z173" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA173" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:27">
+      <c r="A174" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K174" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="O174" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U174" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="175" spans="1:27">
+      <c r="A175" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O175" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q175" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="176" spans="1:27">
+      <c r="A176" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O176" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V176" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W176" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="X176" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="177" spans="1:27">
+      <c r="A177" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L177" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N177" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O177" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P177" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y177" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="178" spans="1:27">
+      <c r="A178" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O178" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z178" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA178" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="179" spans="1:27">
+      <c r="A179" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O179" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z179" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA179" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:27">
+      <c r="A180" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O180" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z180" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA180" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:27">
+      <c r="A181" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O181" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U181" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="182" spans="1:27">
+      <c r="A182" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O182" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q182" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="183" spans="1:27">
+      <c r="A183" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O183" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V183" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W183" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="X183" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="184" spans="1:27">
+      <c r="A184" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L184" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N184" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O184" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P184" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y184" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="185" spans="1:27">
+      <c r="A185" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O185" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z185" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA185" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="186" spans="1:27">
+      <c r="A186" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O186" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z186" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA186" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:27">
+      <c r="A187" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O187" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z187" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA187" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:27">
+      <c r="A188" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K188" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O188" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U188" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:27">
+      <c r="A189" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O189" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q189" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="190" spans="1:27">
+      <c r="A190" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O190" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V190" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W190" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="X190" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="191" spans="1:27">
+      <c r="A191" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L191" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N191" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O191" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P191" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y191" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="192" spans="1:27">
+      <c r="A192" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O192" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z192" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA192" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="193" spans="1:27">
+      <c r="A193" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O193" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z193" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA193" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:27">
+      <c r="A194" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O194" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z194" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA194" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:27">
+      <c r="A195" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K195" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O195" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U195" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:27">
+      <c r="A196" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O196" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q196" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="197" spans="1:27">
+      <c r="A197" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O197" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V197" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W197" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="X197" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="198" spans="1:27">
+      <c r="A198" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J198" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L198" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N198" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O198" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P198" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y198" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="199" spans="1:27">
+      <c r="A199" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O199" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z199" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA199" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="200" spans="1:27">
+      <c r="A200" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O200" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z200" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA200" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:27">
+      <c r="A201" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O201" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z201" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA201" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:27">
+      <c r="A202" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K202" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="O202" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U202" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:27">
+      <c r="A203" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O203" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q203" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="204" spans="1:27">
+      <c r="A204" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O204" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V204" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W204" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="X204" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="205" spans="1:27">
+      <c r="A205" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J205" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L205" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N205" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O205" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P205" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y205" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="206" spans="1:27">
+      <c r="A206" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O206" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z206" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA206" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="207" spans="1:27">
+      <c r="A207" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O207" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z207" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA207" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:27">
+      <c r="A208" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O208" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z208" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA208" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:27">
+      <c r="A209" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K209" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O209" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U209" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="210" spans="1:27">
+      <c r="A210" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O210" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q210" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="211" spans="1:27">
+      <c r="A211" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O211" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V211" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W211" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="X211" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="212" spans="1:27">
+      <c r="A212" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J212" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L212" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N212" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O212" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P212" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y212" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="213" spans="1:27">
+      <c r="A213" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O213" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z213" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA213" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="214" spans="1:27">
+      <c r="A214" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O214" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z214" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA214" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:27">
+      <c r="A215" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O215" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z215" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA215" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:27">
+      <c r="A216" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K216" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O216" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U216" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="217" spans="1:27">
+      <c r="A217" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O217" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q217" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="218" spans="1:27">
+      <c r="A218" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O218" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V218" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W218" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="X218" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="219" spans="1:27">
+      <c r="A219" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J219" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L219" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N219" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O219" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P219" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y219" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="220" spans="1:27">
+      <c r="A220" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O220" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z220" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA220" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="221" spans="1:27">
+      <c r="A221" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O221" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z221" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA221" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:27">
+      <c r="A222" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O222" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z222" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA222" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:27">
+      <c r="A223" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K223" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="O223" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U223" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="224" spans="1:27">
+      <c r="A224" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O224" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q224" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="225" spans="1:27">
+      <c r="A225" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O225" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V225" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W225" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="X225" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="226" spans="1:27">
+      <c r="A226" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D226" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="V106" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="W106" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="X106" s="1" t="s">
+      <c r="F226" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L226" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N226" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O226" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P226" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y226" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="227" spans="1:27">
+      <c r="A227" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O227" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z227" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA227" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="228" spans="1:27">
+      <c r="A228" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O228" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z228" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA228" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:27">
+      <c r="A229" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O229" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z229" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA229" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:27">
+      <c r="A230" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K230" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O230" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U230" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="231" spans="1:27">
+      <c r="A231" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O231" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q231" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="232" spans="1:27">
+      <c r="A232" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O232" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V232" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W232" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="X232" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="233" spans="1:27">
+      <c r="A233" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L233" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N233" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O233" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P233" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y233" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="234" spans="1:27">
+      <c r="A234" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O234" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z234" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA234" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="235" spans="1:27">
+      <c r="A235" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O235" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z235" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA235" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:27">
+      <c r="A236" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O236" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z236" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA236" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:27">
+      <c r="A237" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K237" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O237" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U237" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="238" spans="1:27">
+      <c r="A238" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O238" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q238" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="239" spans="1:27">
+      <c r="A239" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O239" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V239" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W239" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="X239" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="240" spans="1:27">
+      <c r="A240" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D240" s="1" t="s">
         <v>69</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L240" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N240" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O240" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P240" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y240" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="241" spans="1:27">
+      <c r="A241" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O241" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z241" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA241" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="242" spans="1:27">
+      <c r="A242" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O242" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z242" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA242" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:27">
+      <c r="A243" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O243" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z243" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA243" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:27">
+      <c r="A244" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K244" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O244" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U244" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="245" spans="1:27">
+      <c r="A245" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O245" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q245" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="246" spans="1:27">
+      <c r="A246" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O246" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V246" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W246" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="X246" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="247" spans="1:27">
+      <c r="A247" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L247" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N247" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O247" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P247" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y247" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="248" spans="1:27">
+      <c r="A248" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O248" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z248" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA248" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="249" spans="1:27">
+      <c r="A249" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O249" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z249" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA249" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:27">
+      <c r="A250" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O250" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z250" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA250" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:27">
+      <c r="A251" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K251" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O251" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U251" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="252" spans="1:27">
+      <c r="A252" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O252" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q252" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="253" spans="1:27">
+      <c r="A253" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O253" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V253" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W253" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="X253" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="254" spans="1:27">
+      <c r="A254" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J254" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L254" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N254" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O254" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P254" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y254" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="255" spans="1:27">
+      <c r="A255" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O255" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z255" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA255" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="256" spans="1:27">
+      <c r="A256" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O256" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z256" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA256" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:27">
+      <c r="A257" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O257" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z257" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA257" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:27">
+      <c r="A258" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K258" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="O258" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U258" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="259" spans="1:27">
+      <c r="A259" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O259" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q259" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="260" spans="1:27">
+      <c r="A260" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O260" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V260" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W260" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="X260" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="261" spans="1:27">
+      <c r="A261" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J261" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L261" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N261" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O261" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P261" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y261" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="262" spans="1:27">
+      <c r="A262" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O262" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z262" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA262" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="263" spans="1:27">
+      <c r="A263" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O263" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z263" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA263" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:27">
+      <c r="A264" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O264" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z264" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA264" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:27">
+      <c r="A265" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K265" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="O265" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U265" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="266" spans="1:27">
+      <c r="A266" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O266" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q266" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="267" spans="1:27">
+      <c r="A267" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O267" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V267" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W267" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="X267" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="268" spans="1:27">
+      <c r="A268" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J268" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L268" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N268" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O268" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P268" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y268" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="269" spans="1:27">
+      <c r="A269" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O269" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z269" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA269" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="270" spans="1:27">
+      <c r="A270" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O270" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z270" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA270" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:27">
+      <c r="A271" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O271" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z271" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA271" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:27">
+      <c r="A272" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K272" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="O272" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U272" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="273" spans="1:27">
+      <c r="A273" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O273" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q273" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="274" spans="1:27">
+      <c r="A274" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O274" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V274" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W274" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="X274" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="275" spans="1:27">
+      <c r="A275" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F275" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J275" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L275" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N275" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O275" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P275" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y275" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="276" spans="1:27">
+      <c r="A276" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O276" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z276" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA276" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="277" spans="1:27">
+      <c r="A277" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O277" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z277" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA277" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:27">
+      <c r="A278" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O278" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z278" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA278" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:27">
+      <c r="A279" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K279" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="O279" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U279" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="280" spans="1:27">
+      <c r="A280" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O280" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q280" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="281" spans="1:27">
+      <c r="A281" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O281" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V281" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W281" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="X281" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="282" spans="1:27">
+      <c r="A282" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F282" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L282" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N282" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O282" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P282" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y282" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="283" spans="1:27">
+      <c r="A283" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O283" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z283" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA283" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="284" spans="1:27">
+      <c r="A284" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O284" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z284" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA284" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:27">
+      <c r="A285" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O285" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z285" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA285" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:27">
+      <c r="A286" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K286" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O286" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U286" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="287" spans="1:27">
+      <c r="A287" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O287" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q287" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="288" spans="1:27">
+      <c r="A288" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O288" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V288" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W288" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="X288" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="289" spans="1:27">
+      <c r="A289" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F289" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J289" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L289" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N289" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O289" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P289" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y289" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="290" spans="1:27">
+      <c r="A290" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O290" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z290" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA290" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="291" spans="1:27">
+      <c r="A291" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O291" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z291" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA291" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:27">
+      <c r="A292" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O292" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z292" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA292" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:27">
+      <c r="A293" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K293" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O293" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U293" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="294" spans="1:27">
+      <c r="A294" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O294" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q294" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="295" spans="1:27">
+      <c r="A295" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O295" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V295" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W295" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="X295" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="296" spans="1:27">
+      <c r="A296" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F296" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J296" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L296" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N296" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O296" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P296" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y296" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="297" spans="1:27">
+      <c r="A297" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O297" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z297" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA297" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="298" spans="1:27">
+      <c r="A298" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O298" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z298" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA298" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:27">
+      <c r="A299" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O299" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z299" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA299" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:27">
+      <c r="A300" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K300" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="O300" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U300" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="301" spans="1:27">
+      <c r="A301" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O301" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q301" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="302" spans="1:27">
+      <c r="A302" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O302" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V302" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W302" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="X302" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="303" spans="1:27">
+      <c r="A303" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F303" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J303" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L303" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N303" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O303" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P303" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y303" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="304" spans="1:27">
+      <c r="A304" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O304" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z304" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA304" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="305" spans="1:27">
+      <c r="A305" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O305" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z305" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA305" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:27">
+      <c r="A306" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O306" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z306" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA306" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:27">
+      <c r="A307" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K307" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="O307" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U307" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="308" spans="1:27">
+      <c r="A308" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O308" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q308" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="309" spans="1:27">
+      <c r="A309" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O309" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V309" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W309" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="X309" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="310" spans="1:27">
+      <c r="A310" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F310" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J310" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L310" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N310" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O310" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P310" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y310" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="311" spans="1:27">
+      <c r="A311" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O311" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z311" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA311" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="312" spans="1:27">
+      <c r="A312" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O312" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z312" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA312" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:27">
+      <c r="A313" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O313" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z313" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA313" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:27">
+      <c r="A314" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E314" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K314" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O314" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U314" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="315" spans="1:27">
+      <c r="A315" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O315" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q315" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="316" spans="1:27">
+      <c r="A316" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E316" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O316" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V316" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W316" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="X316" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="317" spans="1:27">
+      <c r="A317" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F317" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J317" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L317" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N317" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O317" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P317" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y317" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="318" spans="1:27">
+      <c r="A318" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O318" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z318" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA318" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="319" spans="1:27">
+      <c r="A319" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O319" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z319" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA319" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:27">
+      <c r="A320" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O320" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z320" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA320" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:27">
+      <c r="A321" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E321" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K321" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="O321" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U321" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="322" spans="1:27">
+      <c r="A322" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E322" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O322" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q322" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="323" spans="1:27">
+      <c r="A323" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E323" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O323" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V323" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W323" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="X323" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="324" spans="1:27">
+      <c r="A324" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F324" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J324" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L324" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N324" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O324" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P324" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y324" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="325" spans="1:27">
+      <c r="A325" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O325" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z325" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA325" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="326" spans="1:27">
+      <c r="A326" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O326" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z326" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA326" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:27">
+      <c r="A327" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O327" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z327" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA327" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:27">
+      <c r="A328" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K328" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O328" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U328" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="329" spans="1:27">
+      <c r="A329" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O329" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q329" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="330" spans="1:27">
+      <c r="A330" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O330" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V330" s="1">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W330" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="X330" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
